--- a/All_data/figures/reliability_analysis.xlsx
+++ b/All_data/figures/reliability_analysis.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I9"/>
+  <dimension ref="A1:K9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -466,10 +466,20 @@
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
+          <t>measured CMC 10min</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>measured CMC STD 10min</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
           <t>literature low</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>literature high</t>
         </is>
@@ -500,16 +510,22 @@
         <v>0.25</v>
       </c>
       <c r="H2" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="I2" t="n">
+        <v>0.26</v>
+      </c>
+      <c r="J2" t="n">
         <v>7</v>
       </c>
-      <c r="I2" t="n">
+      <c r="K2" t="n">
         <v>10</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>NaDC</t>
+          <t>DSS</t>
         </is>
       </c>
       <c r="B3" t="n">
@@ -531,9 +547,15 @@
         <v>0.09</v>
       </c>
       <c r="H3" t="n">
+        <v>5.51</v>
+      </c>
+      <c r="I3" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="J3" t="n">
         <v>2.48</v>
       </c>
-      <c r="I3" t="n">
+      <c r="K3" t="n">
         <v>8.199999999999999</v>
       </c>
     </row>
@@ -562,9 +584,15 @@
         <v>0.65</v>
       </c>
       <c r="H4" t="n">
+        <v>15.24</v>
+      </c>
+      <c r="I4" t="n">
+        <v>0.61</v>
+      </c>
+      <c r="J4" t="n">
         <v>13</v>
       </c>
-      <c r="I4" t="n">
+      <c r="K4" t="n">
         <v>15</v>
       </c>
     </row>
@@ -593,9 +621,15 @@
         <v>0.06</v>
       </c>
       <c r="H5" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="I5" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="J5" t="n">
         <v>0.9</v>
       </c>
-      <c r="I5" t="n">
+      <c r="K5" t="n">
         <v>1.24</v>
       </c>
     </row>
@@ -624,9 +658,15 @@
         <v>0.59</v>
       </c>
       <c r="H6" t="n">
+        <v>14.56</v>
+      </c>
+      <c r="I6" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="J6" t="n">
         <v>15.7</v>
       </c>
-      <c r="I6" t="n">
+      <c r="K6" t="n">
         <v>16</v>
       </c>
     </row>
@@ -658,6 +698,12 @@
         <v>3.77</v>
       </c>
       <c r="I7" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="J7" t="n">
+        <v>3.77</v>
+      </c>
+      <c r="K7" t="n">
         <v>4.2</v>
       </c>
     </row>
@@ -686,9 +732,15 @@
         <v>0.15</v>
       </c>
       <c r="H8" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="I8" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="J8" t="n">
         <v>0.28</v>
       </c>
-      <c r="I8" t="n">
+      <c r="K8" t="n">
         <v>0.97</v>
       </c>
     </row>
@@ -717,9 +769,15 @@
         <v>0.43</v>
       </c>
       <c r="H9" t="n">
+        <v>6.99</v>
+      </c>
+      <c r="I9" t="n">
+        <v>0.47</v>
+      </c>
+      <c r="J9" t="n">
         <v>6</v>
       </c>
-      <c r="I9" t="n">
+      <c r="K9" t="n">
         <v>10</v>
       </c>
     </row>
